--- a/laporan_padel_dki_jakarta_2026-10-05.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-05.xlsx
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.580.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp972.000</t>
+          <t>Rp1.134.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp19.300.000</t>
+          <t>Rp20.100.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.562.000</t>
+          <t>Rp4.724.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.949.994</t>
+          <t>Rp3.074.994</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-05.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-05.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp860.000</t>
+          <t>Rp940.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>176</v>
       </c>
       <c r="D4" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.740.000</t>
+          <t>Rp4.440.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp715.000</t>
+          <t>Rp325.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp9.540.000</t>
+          <t>Rp9.640.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.743.000</t>
+          <t>Rp2.241.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp14.100.000</t>
+          <t>Rp14.430.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp124.000</t>
+          <t>Rp266.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp425.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.608.000</t>
+          <t>Rp9.808.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp11.405.000</t>
+          <t>Rp11.481.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.724.000</t>
+          <t>Rp4.805.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.925.000</t>
+          <t>Rp14.125.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7607,14 +7607,14 @@
         </is>
       </c>
       <c r="C41" t="n">
+        <v>75</v>
+      </c>
+      <c r="D41" t="n">
         <v>65</v>
       </c>
-      <c r="D41" t="n">
-        <v>55</v>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp350.000</t>
+          <t>Rp100.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -7672,16 +7672,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.550.000</t>
+          <t>Rp8.815.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp6.810.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp1.510.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.174.996</t>
+          <t>Rp3.424.996</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.074.994</t>
+          <t>Rp2.949.994</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp120.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-05.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-05.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp749.000</t>
+          <t>Rp1.274.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.240.000</t>
+          <t>Rp5.680.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.950.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.028.000</t>
+          <t>Rp6.634.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp12.870.000</t>
+          <t>Rp13.120.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>168</v>
       </c>
       <c r="D22" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp8.350.000</t>
+          <t>Rp8.549.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp325.000</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.842.000</t>
+          <t>Rp9.642.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp498.000</t>
+          <t>Rp647.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp2.510.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp660.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp498.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>102</v>
       </c>
       <c r="D71" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.762.500</t>
+          <t>Rp3.637.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp4.565.000</t>
+          <t>Rp4.045.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp992.000</t>
+          <t>Rp1.091.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>64</v>
       </c>
       <c r="D96" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.092.000</t>
+          <t>Rp11.327.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.640.000</t>
+          <t>Rp1.840.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.640.000</t>
+          <t>Rp4.430.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp849.000</t>
+          <t>Rp999.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.480.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.197.000</t>
+          <t>Rp1.397.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.241.000</t>
+          <t>Rp2.988.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp14.430.000</t>
+          <t>Rp14.605.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp2.775.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D63" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp7.550.000</t>
+          <t>Rp7.950.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>30</v>
       </c>
       <c r="D68" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.540.000</t>
+          <t>Rp2.190.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp20.100.000</t>
+          <t>Rp20.350.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.120.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.185.000</t>
+          <t>Rp4.410.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp336.000</t>
+          <t>Rp504.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp5.960.000</t>
+          <t>Rp5.460.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>106</v>
       </c>
       <c r="D3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.820.000</t>
+          <t>Rp10.100.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp8.845.000</t>
+          <t>Rp9.620.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp11.481.000</t>
+          <t>Rp11.421.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.425.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp14.350.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.683.000</t>
+          <t>Rp1.782.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp297.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.805.000</t>
+          <t>Rp4.886.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.394.000</t>
+          <t>Rp3.194.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp199.000 - Rp275.000</t>
+          <t>Rp170.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -7145,16 +7145,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp675.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7207,21 +7207,21 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp550.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp345.000</t>
+          <t>Rp150.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -7266,14 +7266,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp175.000</t>
+          <t>Rp90.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp14.125.000</t>
+          <t>Rp14.225.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp12.447.000</t>
+          <t>Rp13.247.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.575.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp535.000</t>
+          <t>Rp735.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp520.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.424.996</t>
+          <t>Rp4.074.994</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.380.000</t>
+          <t>Rp18.860.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp975.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.460.000</t>
+          <t>Rp2.658.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp185.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp693.000</t>
+          <t>Rp1.092.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp544.000</t>
+          <t>Rp1.558.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp120.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-05.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-05.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.180.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,21 +575,21 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp942.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp199.000</t>
+          <t>Rp99.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp358.000</t>
+          <t>Rp1.168.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.684.987</t>
+          <t>Rp4.335.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.634.000</t>
+          <t>Rp8.490.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp1.472.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.209.000</t>
+          <t>Rp1.389.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.672.000</t>
+          <t>Rp3.867.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.110.000</t>
+          <t>Rp4.730.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.580.000</t>
+          <t>Rp4.830.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp870.000</t>
+          <t>Rp1.290.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.642.000</t>
+          <t>Rp9.292.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.814.000</t>
+          <t>Rp3.512.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp864.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>28</v>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp9.640.000</t>
+          <t>Rp9.740.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.510.000</t>
+          <t>Rp3.210.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>32</v>
       </c>
       <c r="D68" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.360.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>102</v>
       </c>
       <c r="D71" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp3.637.500</t>
+          <t>Rp2.637.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp3.130.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.091.000</t>
+          <t>Rp892.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp6.275.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp3.120.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp1.325.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>64</v>
       </c>
       <c r="D96" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.730.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>28</v>
       </c>
       <c r="D99" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.134.000</t>
+          <t>Rp1.215.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.327.000</t>
+          <t>Rp11.612.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp999.000</t>
+          <t>Rp1.299.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.920.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.397.000</t>
+          <t>Rp1.746.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.290.000</t>
+          <t>Rp3.640.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.988.000</t>
+          <t>Rp3.237.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>77</v>
       </c>
       <c r="D43" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.750.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.775.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.168.000</t>
+          <t>Rp3.960.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D64" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.079.000</t>
+          <t>Rp2.673.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>30</v>
       </c>
       <c r="D67" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp250.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp504.000</t>
+          <t>Rp960.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp998.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp5.460.000</t>
+          <t>Rp5.860.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>106</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.150.000</t>
+          <t>Rp8.150.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.100.000</t>
+          <t>Rp11.100.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp397.000</t>
+          <t>Rp466.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp9.620.000</t>
+          <t>Rp10.620.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.808.000</t>
+          <t>Rp9.708.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp11.421.000</t>
+          <t>Rp12.261.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.949.000</t>
+          <t>Rp5.507.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.975.000</t>
+          <t>Rp12.275.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.925.000</t>
+          <t>Rp4.875.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.782.000</t>
+          <t>Rp2.079.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7080,14 +7080,14 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>60</v>
       </c>
       <c r="D29" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.270.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>91</v>
       </c>
       <c r="D30" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.910.000</t>
+          <t>Rp3.340.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp12.360.000</t>
+          <t>Rp13.830.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp14.225.000</t>
+          <t>Rp15.675.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.932.000</t>
+          <t>Rp4.796.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp868.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp13.247.000</t>
+          <t>Rp10.047.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.815.000</t>
+          <t>Rp9.610.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp26.600.000</t>
+          <t>Rp27.800.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7820,28 +7820,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Let's Go Padel Sunter</t>
+          <t>House of Mayor</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="D48" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp6.810.000</t>
+          <t>Rp8.376.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp350.000</t>
+          <t>Rp229.000 - Rp349.000</t>
         </is>
       </c>
     </row>
@@ -7851,28 +7851,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Padre Padel Kelapa Gading</t>
+          <t>Let's Go Padel Sunter</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D49" t="n">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp7.490.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp175.000</t>
+          <t>Rp150.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -7882,26 +7882,57 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>Padre Padel Kelapa Gading</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>144</v>
+      </c>
+      <c r="D50" t="n">
+        <v>120</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rp4.100.000</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Rp125.000 - Rp175.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>wePADL at Meridian Sports &amp; Wellness (MSW) PIK</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C51" t="n">
         <v>90</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D51" t="n">
         <v>71</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>21.1%</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Rp4.600.000</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Rp75.000 - Rp300.000</t>
         </is>
@@ -8064,16 +8095,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8095,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.787.000</t>
+          <t>Rp2.292.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8157,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp185.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8219,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.180.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.580.000</t>
+          <t>Rp5.805.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8374,16 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8405,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8436,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp495.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8467,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.520.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8498,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8560,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.860.000</t>
+          <t>Rp19.820.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8653,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp975.000</t>
+          <t>Rp1.170.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8684,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp270.000</t>
+          <t>Rp668.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8746,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.285.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8870,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp675.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8963,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.155.000</t>
+          <t>Rp2.955.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9025,16 +9056,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.658.000</t>
+          <t>Rp2.758.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9211,16 +9242,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp840.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -9242,16 +9273,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-05.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-05.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.274.000</t>
+          <t>Rp1.674.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.168.000</t>
+          <t>Rp898.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.680.000</t>
+          <t>Rp6.640.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.335.988</t>
+          <t>Rp5.033.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.875.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>170</v>
       </c>
       <c r="D17" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.530.000</t>
+          <t>Rp6.830.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.830.000</t>
+          <t>Rp5.330.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp975.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp4.440.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp9.740.000</t>
+          <t>Rp9.840.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp498.000</t>
+          <t>Rp996.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>102</v>
       </c>
       <c r="D71" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.637.500</t>
+          <t>Rp3.137.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp6.275.000</t>
+          <t>Rp6.950.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.580.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp625.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp266.000</t>
+          <t>Rp399.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D64" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.673.000</t>
+          <t>Rp3.267.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.690.000</t>
+          <t>Rp5.025.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp3.970.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp5.860.000</t>
+          <t>Rp5.780.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>106</v>
       </c>
       <c r="D3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.150.000</t>
+          <t>Rp8.270.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp466.000</t>
+          <t>Rp535.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.275.000</t>
+          <t>Rp12.575.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.200.000</t>
+          <t>Rp20.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.886.000</t>
+          <t>Rp3.092.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>60</v>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.270.000</t>
+          <t>Rp3.930.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>91</v>
       </c>
       <c r="D30" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.340.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp376.000</t>
+          <t>Rp952.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.805.000</t>
+          <t>Rp6.230.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.390.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.175.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-05.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-05.xlsx
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.380.000</t>
+          <t>Rp2.680.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.867.000</t>
+          <t>Rp3.267.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.612.000</t>
+          <t>Rp12.010.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp425.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.575.000</t>
+          <t>Rp12.725.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.800.000</t>
+          <t>Rp20.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.092.000</t>
+          <t>Rp3.292.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.949.994</t>
+          <t>Rp3.074.994</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.758.000</t>
+          <t>Rp2.956.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
